--- a/Data/final_tables/supplementary_file_2_BARD1_all_reagents.xlsx
+++ b/Data/final_tables/supplementary_file_2_BARD1_all_reagents.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/BARD1_SGE_analysis/Data/final_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B5C1CD-CB2C-D847-8988-8190E236C6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB6212C-F38E-224B-827F-E7DCA9DEFE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16100" activeTab="5" xr2:uid="{D2A65EDD-B858-E447-8FDB-B7AA24207239}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16100" xr2:uid="{D2A65EDD-B858-E447-8FDB-B7AA24207239}"/>
   </bookViews>
   <sheets>
-    <sheet name="all_reagents" sheetId="6" r:id="rId1"/>
-    <sheet name="sge_oligos" sheetId="1" r:id="rId2"/>
-    <sheet name="dna_pcr1_primers" sheetId="2" r:id="rId3"/>
-    <sheet name="dna_pcr2_primers" sheetId="3" r:id="rId4"/>
-    <sheet name="rna_isoform_primers" sheetId="5" r:id="rId5"/>
-    <sheet name="rna_preseq_primers" sheetId="4" r:id="rId6"/>
+    <sheet name="README" sheetId="7" r:id="rId1"/>
+    <sheet name="all_reagents" sheetId="6" r:id="rId2"/>
+    <sheet name="sge_oligos" sheetId="1" r:id="rId3"/>
+    <sheet name="dna_pcr1_primers" sheetId="2" r:id="rId4"/>
+    <sheet name="dna_pcr2_primers" sheetId="3" r:id="rId5"/>
+    <sheet name="rna_isoform_primers" sheetId="5" r:id="rId6"/>
+    <sheet name="rna_preseq_primers" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="1273">
   <si>
     <t>Oligo Name</t>
   </si>
@@ -5413,13 +5414,318 @@
   </si>
   <si>
     <t>GATTCAAAGACAAATATGAATGACTCT</t>
+  </si>
+  <si>
+    <t>This tab is formatted as follows:</t>
+  </si>
+  <si>
+    <t>tab_name</t>
+  </si>
+  <si>
+    <t>tab description</t>
+  </si>
+  <si>
+    <t>column_name</t>
+  </si>
+  <si>
+    <t>column description</t>
+  </si>
+  <si>
+    <t>all_reagents</t>
+  </si>
+  <si>
+    <t>Catalog of all reagents and materials used</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>Reagent/material name</t>
+  </si>
+  <si>
+    <t>Supplier/manufacturer</t>
+  </si>
+  <si>
+    <t>If applicable, catalog number of the product</t>
+  </si>
+  <si>
+    <t>sge_oligos</t>
+  </si>
+  <si>
+    <t>Catalog of all oligonucleotides designed and ordered for cloning variant libraries. Table is grouped by SGE region with a line break between each section</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">the name of the SGE library containing the variant. In cases where an entire exon is covered by a single SGE library, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">target </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> exon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> will be the same. In cases where exons are covered by multiple SGE libraries, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t>target</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> will equal to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t>exon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> plus a single letter (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t>A, B, C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…) appended to the name. As an example, BARD1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t>_X7B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> represents the second (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) tile of exon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> BARD1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. </t>
+    </r>
+  </si>
+  <si>
+    <t>Name of the oligo. All oligos named with Region_OligoName.  Description of all oligos is below:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sgeoligo is the base sequence upon which all SNVs and 3bp deletions were generated. Fixed edits are in lower case. </t>
+  </si>
+  <si>
+    <t>Oligos with AMP suffix were used to amplify the library from the pooled array. F/R denote forward and reverse primers</t>
+  </si>
+  <si>
+    <t>LIN suffix oligos were used to linerarize the homology arm pUC-19 plasmid. 3/5 denote forward and reverse primers</t>
+  </si>
+  <si>
+    <t>sgRNA suffix oligos are the sequences of the guides designed for the region. 1/2 denote if this was the first or second choice guide (as determined by on/off-target scores). Some regions only have on guide designed. W/C denote the Watson/Crick strand of the guide oligo duplex.</t>
+  </si>
+  <si>
+    <t>HA suffix oligos were PCR primers used to amplify homology arms out of WT HAP1 gDNA. F/R denote forward and reverse primers</t>
+  </si>
+  <si>
+    <t>PUC19 suffix oligos are identical to the HA primers but with an added adapter to add sequence homology to the pUC19 backbone for cloning</t>
+  </si>
+  <si>
+    <t>Sequence of the oligo</t>
+  </si>
+  <si>
+    <t>dna_pcr1_primers</t>
+  </si>
+  <si>
+    <t>Catalog of all primers used for the first pre-sequencing reaction for DNA samples</t>
+  </si>
+  <si>
+    <t>Name of the oligo. Typically they are: BARD1_Region_Primer_name. Generally, the same primers pairs were used for all targets within an exon except for exon 4. F/R denote forward/reverse. Ext/Seqout denotes if the primer was designed to be outside the homology arm or within it respectively</t>
+  </si>
+  <si>
+    <t>dna_pcr2_primers</t>
+  </si>
+  <si>
+    <t>Catalog of all primers used for the second pre-sequencing reaction for DNA samples</t>
+  </si>
+  <si>
+    <t>Denotes if primer is a forward (FWD) or reverse (REV) primer</t>
+  </si>
+  <si>
+    <t>sequence Name</t>
+  </si>
+  <si>
+    <t>Name of oligo. Typically they are: SGE region following by the Illumina adapter added</t>
+  </si>
+  <si>
+    <t>Primer sequence</t>
+  </si>
+  <si>
+    <t>rna_isoform_primers</t>
+  </si>
+  <si>
+    <t>Primers used in RT-PCR to determine if alternate splicing of BARD1 occurred in HAP1 cells</t>
+  </si>
+  <si>
+    <t>keys</t>
+  </si>
+  <si>
+    <t>Name of primer. They are BARD1 following by the exons the forward/reverse primers exist in, followed by for/rev. For example, BARD1_ex1_4cDNA_for is the forward primer of the pair amplifying exons 1 through 4</t>
+  </si>
+  <si>
+    <t>Name of the primer as shown in supplmentary figure S7A</t>
+  </si>
+  <si>
+    <t>Catalog of all primers used in all PCR reactions to prepare RNA samples for sequencing</t>
+  </si>
+  <si>
+    <t>rna_preseq_primers</t>
+  </si>
+  <si>
+    <t>Denotes the exon that will be amplified</t>
+  </si>
+  <si>
+    <t>Name of the oligo. Oligos are named as follow:</t>
+  </si>
+  <si>
+    <t>BARD1_{exon/targets}_RNA_{PCR1/2}_{Fwd/Rev}</t>
+  </si>
+  <si>
+    <t>For all exons except 4 and 11, only PCR2 primers exist. For Exons 4 and 11, PCR2 primers also denote the SGE targets they amplify while the PCR1 primer onlly specifies the whole exon</t>
+  </si>
+  <si>
+    <t>PCR1 primers were designed exon 4 and 11 due to size and named accordingly</t>
+  </si>
+  <si>
+    <t>Fwd/Rev denotes forward or reverse primer</t>
+  </si>
+  <si>
+    <t>Full Sequence</t>
+  </si>
+  <si>
+    <t>Sequence of the oligo. For all PCR2 primers, Illumina Truseq and Nextera adapters have been added.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5498,6 +5804,26 @@
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5519,7 +5845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5530,6 +5856,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5863,6 +6196,331 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF6C2BE-23C1-2E44-9291-C9C391AAC0E7}">
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="153" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>764</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="188" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>813</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>814</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C699ACFC-0356-CB48-84EB-CA98E60787B9}">
   <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6299,7 +6957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320415C2-128F-CE40-A1FB-87572F7BBF9E}">
   <dimension ref="A1:C463"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -9856,7 +10514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC976FB-E376-9B4F-8E7B-B520354377B7}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -10070,7 +10728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F3AB07-91A1-C94C-8381-8B82208A978E}">
   <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -11051,7 +11709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D18ED8-3758-7141-A8BB-1CD9705EDEE3}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -11142,7 +11800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836E4276-24F7-6141-B4D6-D34B72FAD530}">
   <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
